--- a/examples/Rivastigmine/CEREBRO_X_Completed_Data_Rivastigmine.xlsx
+++ b/examples/Rivastigmine/CEREBRO_X_Completed_Data_Rivastigmine.xlsx
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-05T08:08:02Z  | Pipeline: v20  | Source: CEREBRO_Input_Rivastigmine.xlsx</t>
+          <t>Generated: 2026-09-05T19:54:06Z  | Pipeline: v20  | Source: CEREBRO_Input_Rivastigmine.xlsx</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>82.97</v>
+        <v>82.87</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>81.95999999999999</v>
+        <v>81.89</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>81.73999999999999</v>
+        <v>81.62</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0805</v>
+        <v>0.0907</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>Full QM tunneling (QCElemental + ASE): surrogate score 16.09 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full QM tunneling (QCElemental + ASE): surrogate score 18.14 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="C14" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>Full radical-chain reaction MD: surrogate score 58.26 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full radical-chain reaction MD: surrogate score 57.8 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0805</v>
+        <v>0.0907</v>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>Full QM tunneling (QCElemental + ASE): surrogate score 16.09 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full QM tunneling (QCElemental + ASE): surrogate score 18.14 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>35.76</v>
+        <v>35.3</v>
       </c>
       <c r="C27" t="n">
-        <v>35.76</v>
+        <v>35.3</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>Full radical-chain reaction MD: surrogate score 35.76 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full radical-chain reaction MD: surrogate score 35.3 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0805</v>
+        <v>0.0907</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t>Full QM tunneling (QCElemental + ASE): surrogate score 16.09 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full QM tunneling (QCElemental + ASE): surrogate score 18.14 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>35.76</v>
+        <v>35.3</v>
       </c>
       <c r="C41" t="n">
-        <v>35.76</v>
+        <v>35.3</v>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="F41" s="22" t="inlineStr">
         <is>
-          <t>Full radical-chain reaction MD: surrogate score 35.76 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full radical-chain reaction MD: surrogate score 35.3 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -9588,11 +9588,11 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>83.05</v>
+        <v>83.97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>83.97</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -9624,11 +9624,11 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -9696,11 +9696,11 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>72.54000000000001</v>
+        <v>70.56</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>70.56</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -9768,11 +9768,11 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -9984,11 +9984,11 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -10128,11 +10128,11 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>87.98</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -10200,11 +10200,11 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>61.59</v>
+        <v>61.29</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>61.59</t>
+          <t>61.29</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -10236,11 +10236,11 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>64.25</v>
+        <v>64.47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>64.25</t>
+          <t>64.47</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -10308,11 +10308,11 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>89.95</v>
+        <v>89.98</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -11611,21 +11611,21 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr">
         <is>
-          <t>Resolved clinical half-life (bundle tier 1); Mahmood 2007 exponents shown for re</t>
+          <t>Resolved clinical half-life (bundle tier 6); Mahmood 2007 exponents shown for re</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -11647,11 +11647,11 @@
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -11683,11 +11683,11 @@
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -11971,11 +11971,11 @@
         </is>
       </c>
       <c r="D74" s="7" t="n">
-        <v>89.95</v>
+        <v>89.98</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -12331,11 +12331,11 @@
         </is>
       </c>
       <c r="D84" s="7" t="n">
-        <v>79.2</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -13332,28 +13332,28 @@
         <v>1</v>
       </c>
       <c r="AN4" s="28" t="n">
-        <v>82.97</v>
+        <v>82.87</v>
       </c>
       <c r="AO4" s="28" t="n">
-        <v>87.79000000000001</v>
+        <v>87.59</v>
       </c>
       <c r="AP4" s="28" t="n">
-        <v>58.39</v>
+        <v>57.47</v>
       </c>
       <c r="AQ4" s="28" t="n">
-        <v>71.14</v>
+        <v>71.06</v>
       </c>
       <c r="AR4" s="28" t="n">
-        <v>91.56</v>
+        <v>91.59</v>
       </c>
       <c r="AS4" s="28" t="n">
         <v>61.67</v>
       </c>
       <c r="AT4" s="28" t="n">
-        <v>81</v>
+        <v>80.97</v>
       </c>
       <c r="AU4" s="28" t="n">
-        <v>65.76000000000001</v>
+        <v>65.94</v>
       </c>
       <c r="AV4" s="28" t="n">
         <v>0</v>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="AY4" s="28" t="n">
-        <v>79.02</v>
+        <v>78.92</v>
       </c>
       <c r="AZ4" s="28" t="inlineStr">
         <is>
@@ -13573,28 +13573,28 @@
         <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>81.95999999999999</v>
+        <v>81.89</v>
       </c>
       <c r="AO5" t="n">
-        <v>87.69</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>58.65</v>
+        <v>57.72</v>
       </c>
       <c r="AQ5" t="n">
-        <v>68.59999999999999</v>
+        <v>68.52</v>
       </c>
       <c r="AR5" t="n">
-        <v>91.77</v>
+        <v>91.8</v>
       </c>
       <c r="AS5" t="n">
         <v>56.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>73.18000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>69.51000000000001</v>
+        <v>69.69</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>78.06</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -13814,28 +13814,28 @@
         <v>3</v>
       </c>
       <c r="AN6" t="n">
-        <v>81.73999999999999</v>
+        <v>81.62</v>
       </c>
       <c r="AO6" t="n">
-        <v>87.15000000000001</v>
+        <v>86.92</v>
       </c>
       <c r="AP6" t="n">
-        <v>58.9</v>
+        <v>57.98</v>
       </c>
       <c r="AQ6" t="n">
-        <v>68.59999999999999</v>
+        <v>68.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>91.18000000000001</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="AS6" t="n">
         <v>56.67</v>
       </c>
       <c r="AT6" t="n">
-        <v>72.84999999999999</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>69.51000000000001</v>
+        <v>69.69</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>77.84</v>
+        <v>77.73</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -14055,28 +14055,28 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>80.98</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AO7" t="n">
-        <v>88.8</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="AP7" t="n">
-        <v>58.77</v>
+        <v>57.85</v>
       </c>
       <c r="AQ7" t="n">
-        <v>51.17</v>
+        <v>51.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>91.41</v>
+        <v>91.44</v>
       </c>
       <c r="AS7" t="n">
         <v>65</v>
       </c>
       <c r="AT7" t="n">
-        <v>68.3</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>67.95</v>
+        <v>68.13</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>77.13</v>
+        <v>77.05</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
@@ -14296,28 +14296,28 @@
         <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>80.20999999999999</v>
+        <v>80.13</v>
       </c>
       <c r="AO8" t="n">
-        <v>87.18000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="AP8" t="n">
-        <v>58.51</v>
+        <v>57.59</v>
       </c>
       <c r="AQ8" t="n">
-        <v>51.17</v>
+        <v>51.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>92.16</v>
+        <v>92.19</v>
       </c>
       <c r="AS8" t="n">
         <v>65</v>
       </c>
       <c r="AT8" t="n">
-        <v>68.95999999999999</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>66.7</v>
+        <v>66.88</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>76.39</v>
+        <v>76.31</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
@@ -14537,28 +14537,28 @@
         <v>6</v>
       </c>
       <c r="AN9" t="n">
-        <v>75.09</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AO9" t="n">
-        <v>86.86</v>
+        <v>86.73</v>
       </c>
       <c r="AP9" t="n">
         <v>58.44</v>
       </c>
       <c r="AQ9" t="n">
-        <v>50.06</v>
+        <v>49.99</v>
       </c>
       <c r="AR9" t="n">
-        <v>90.37</v>
+        <v>90.41</v>
       </c>
       <c r="AS9" t="n">
         <v>55</v>
       </c>
       <c r="AT9" t="n">
-        <v>69.68000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>66.38</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -14572,7 +14572,7 @@
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>75.09</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
@@ -14778,28 +14778,28 @@
         <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>74.7</v>
+        <v>74.59</v>
       </c>
       <c r="AO10" t="n">
-        <v>70.76000000000001</v>
+        <v>70.47</v>
       </c>
       <c r="AP10" t="n">
-        <v>58.39</v>
+        <v>57.47</v>
       </c>
       <c r="AQ10" t="n">
-        <v>71.14</v>
+        <v>71.06</v>
       </c>
       <c r="AR10" t="n">
-        <v>90.22</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="AS10" t="n">
         <v>57.67</v>
       </c>
       <c r="AT10" t="n">
-        <v>78.23</v>
+        <v>78.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>66.38</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -14813,7 +14813,7 @@
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>71.14</v>
+        <v>71.03</v>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
@@ -15019,28 +15019,28 @@
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>69.78</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="AO11" t="n">
-        <v>74.93000000000001</v>
+        <v>74.91</v>
       </c>
       <c r="AP11" t="n">
         <v>58.44</v>
       </c>
       <c r="AQ11" t="n">
-        <v>50.06</v>
+        <v>49.99</v>
       </c>
       <c r="AR11" t="n">
-        <v>90.7</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="AS11" t="n">
         <v>51.73</v>
       </c>
       <c r="AT11" t="n">
-        <v>70.68000000000001</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>67.63</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>69.78</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
@@ -15567,28 +15567,28 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>82.97</v>
+        <v>82.87</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>87.79000000000001</v>
+        <v>87.59</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>58.39</v>
+        <v>57.47</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>71.14</v>
+        <v>71.06</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>91.56</v>
+        <v>91.59</v>
       </c>
       <c r="H5" s="32" t="n">
         <v>61.67</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>81</v>
+        <v>80.97</v>
       </c>
       <c r="J5" s="32" t="n">
-        <v>65.76000000000001</v>
+        <v>65.94</v>
       </c>
       <c r="K5" s="32" t="n">
         <v>61.98</v>
@@ -15597,22 +15597,22 @@
         <v>100</v>
       </c>
       <c r="M5" s="30" t="n">
-        <v>83.05</v>
+        <v>83.97</v>
       </c>
       <c r="N5" s="33" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="O5" s="32" t="n">
         <v>70</v>
       </c>
       <c r="P5" s="32" t="n">
-        <v>72.54000000000001</v>
+        <v>70.56</v>
       </c>
       <c r="Q5" s="30" t="n">
         <v>100</v>
       </c>
       <c r="R5" s="31" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="S5" s="30" t="n">
         <v>100</v>
@@ -15630,7 +15630,7 @@
         <v>100</v>
       </c>
       <c r="X5" s="30" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="Y5" s="30" t="n">
         <v>85.09999999999999</v>
@@ -15642,22 +15642,22 @@
         <v>86.25</v>
       </c>
       <c r="AB5" s="30" t="n">
-        <v>87.98</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="AC5" s="30" t="n">
         <v>100</v>
       </c>
       <c r="AD5" s="32" t="n">
-        <v>61.59</v>
+        <v>61.29</v>
       </c>
       <c r="AE5" s="32" t="n">
-        <v>64.25</v>
+        <v>64.47</v>
       </c>
       <c r="AF5" s="30" t="n">
         <v>88</v>
       </c>
       <c r="AG5" s="30" t="n">
-        <v>89.95</v>
+        <v>89.98</v>
       </c>
       <c r="AH5" s="30" t="n">
         <v>100</v>
@@ -15772,28 +15772,28 @@
         </is>
       </c>
       <c r="C6" s="28" t="n">
-        <v>81.95999999999999</v>
+        <v>81.89</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>87.69</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="E6" s="31" t="n">
-        <v>58.65</v>
+        <v>57.72</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>68.59999999999999</v>
+        <v>68.52</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>91.77</v>
+        <v>91.8</v>
       </c>
       <c r="H6" s="31" t="n">
         <v>56.67</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>73.18000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>69.51000000000001</v>
+        <v>69.69</v>
       </c>
       <c r="K6" s="31" t="n">
         <v>54.9</v>
@@ -15802,22 +15802,22 @@
         <v>100</v>
       </c>
       <c r="M6" s="30" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="N6" s="33" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="O6" s="32" t="n">
         <v>70</v>
       </c>
       <c r="P6" s="30" t="n">
-        <v>90.84999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="Q6" s="30" t="n">
         <v>80</v>
       </c>
       <c r="R6" s="34" t="n">
-        <v>35.76</v>
+        <v>35.3</v>
       </c>
       <c r="S6" s="30" t="n">
         <v>100</v>
@@ -15835,7 +15835,7 @@
         <v>100</v>
       </c>
       <c r="X6" s="30" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="Y6" s="32" t="n">
         <v>70.92</v>
@@ -15847,16 +15847,16 @@
         <v>83.75</v>
       </c>
       <c r="AB6" s="30" t="n">
-        <v>81.73</v>
+        <v>81.34</v>
       </c>
       <c r="AC6" s="30" t="n">
         <v>100</v>
       </c>
       <c r="AD6" s="32" t="n">
-        <v>70.59</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="AE6" s="32" t="n">
-        <v>73.41</v>
+        <v>73.66</v>
       </c>
       <c r="AF6" s="30" t="n">
         <v>88</v>
@@ -15977,28 +15977,28 @@
         </is>
       </c>
       <c r="C7" s="28" t="n">
-        <v>81.73999999999999</v>
+        <v>81.62</v>
       </c>
       <c r="D7" s="30" t="n">
-        <v>87.15000000000001</v>
+        <v>86.92</v>
       </c>
       <c r="E7" s="31" t="n">
-        <v>58.9</v>
+        <v>57.98</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>68.59999999999999</v>
+        <v>68.52</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>91.18000000000001</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="H7" s="31" t="n">
         <v>56.67</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>72.84999999999999</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="J7" s="32" t="n">
-        <v>69.51000000000001</v>
+        <v>69.69</v>
       </c>
       <c r="K7" s="31" t="n">
         <v>54.9</v>
@@ -16007,22 +16007,22 @@
         <v>100</v>
       </c>
       <c r="M7" s="30" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="N7" s="33" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="O7" s="32" t="n">
         <v>70</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>78.65000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Q7" s="30" t="n">
         <v>80</v>
       </c>
       <c r="R7" s="34" t="n">
-        <v>35.76</v>
+        <v>35.3</v>
       </c>
       <c r="S7" s="30" t="n">
         <v>100</v>
@@ -16040,7 +16040,7 @@
         <v>100</v>
       </c>
       <c r="X7" s="30" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="Y7" s="32" t="n">
         <v>70.92</v>
@@ -16052,16 +16052,16 @@
         <v>83.75</v>
       </c>
       <c r="AB7" s="30" t="n">
-        <v>86.02</v>
+        <v>84.86</v>
       </c>
       <c r="AC7" s="30" t="n">
         <v>100</v>
       </c>
       <c r="AD7" s="32" t="n">
-        <v>67.59</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="AE7" s="32" t="n">
-        <v>68.67</v>
+        <v>68.91</v>
       </c>
       <c r="AF7" s="30" t="n">
         <v>88</v>
@@ -16182,28 +16182,28 @@
         </is>
       </c>
       <c r="C8" s="28" t="n">
-        <v>80.98</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D8" s="30" t="n">
-        <v>88.8</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="E8" s="31" t="n">
-        <v>58.77</v>
+        <v>57.85</v>
       </c>
       <c r="F8" s="31" t="n">
-        <v>51.17</v>
+        <v>51.1</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>91.41</v>
+        <v>91.44</v>
       </c>
       <c r="H8" s="32" t="n">
         <v>65</v>
       </c>
       <c r="I8" s="32" t="n">
-        <v>68.3</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="J8" s="32" t="n">
-        <v>67.95</v>
+        <v>68.13</v>
       </c>
       <c r="K8" s="31" t="n">
         <v>54.73</v>
@@ -16212,22 +16212,22 @@
         <v>100</v>
       </c>
       <c r="M8" s="30" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="N8" s="33" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="O8" s="32" t="n">
         <v>70</v>
       </c>
       <c r="P8" s="30" t="n">
-        <v>84.75</v>
+        <v>83.64</v>
       </c>
       <c r="Q8" s="30" t="n">
         <v>100</v>
       </c>
       <c r="R8" s="33" t="n">
-        <v>13.26</v>
+        <v>12.8</v>
       </c>
       <c r="S8" s="30" t="n">
         <v>100</v>
@@ -16245,7 +16245,7 @@
         <v>100</v>
       </c>
       <c r="X8" s="30" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="Y8" s="31" t="n">
         <v>42.55</v>
@@ -16257,16 +16257,16 @@
         <v>85</v>
       </c>
       <c r="AB8" s="30" t="n">
-        <v>87.98</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="AC8" s="30" t="n">
         <v>100</v>
       </c>
       <c r="AD8" s="32" t="n">
-        <v>67.59</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="AE8" s="32" t="n">
-        <v>69.25</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AF8" s="30" t="n">
         <v>88</v>
@@ -16387,28 +16387,28 @@
         </is>
       </c>
       <c r="C9" s="28" t="n">
-        <v>80.20999999999999</v>
+        <v>80.13</v>
       </c>
       <c r="D9" s="30" t="n">
-        <v>87.18000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="E9" s="31" t="n">
-        <v>58.51</v>
+        <v>57.59</v>
       </c>
       <c r="F9" s="31" t="n">
-        <v>51.17</v>
+        <v>51.1</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>92.16</v>
+        <v>92.19</v>
       </c>
       <c r="H9" s="32" t="n">
         <v>65</v>
       </c>
       <c r="I9" s="32" t="n">
-        <v>68.95999999999999</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>66.7</v>
+        <v>66.88</v>
       </c>
       <c r="K9" s="31" t="n">
         <v>54.73</v>
@@ -16417,22 +16417,22 @@
         <v>100</v>
       </c>
       <c r="M9" s="32" t="n">
-        <v>78.05</v>
+        <v>78.97</v>
       </c>
       <c r="N9" s="33" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="O9" s="32" t="n">
         <v>70</v>
       </c>
       <c r="P9" s="30" t="n">
-        <v>84.75</v>
+        <v>83.64</v>
       </c>
       <c r="Q9" s="30" t="n">
         <v>100</v>
       </c>
       <c r="R9" s="33" t="n">
-        <v>13.26</v>
+        <v>12.8</v>
       </c>
       <c r="S9" s="30" t="n">
         <v>100</v>
@@ -16450,7 +16450,7 @@
         <v>100</v>
       </c>
       <c r="X9" s="30" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="Y9" s="31" t="n">
         <v>42.55</v>
@@ -16462,16 +16462,16 @@
         <v>85</v>
       </c>
       <c r="AB9" s="30" t="n">
-        <v>81.73</v>
+        <v>81.34</v>
       </c>
       <c r="AC9" s="30" t="n">
         <v>100</v>
       </c>
       <c r="AD9" s="32" t="n">
-        <v>73.59</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="AE9" s="32" t="n">
-        <v>75.27</v>
+        <v>75.53</v>
       </c>
       <c r="AF9" s="30" t="n">
         <v>88</v>
@@ -16592,28 +16592,28 @@
         </is>
       </c>
       <c r="C10" s="35" t="n">
-        <v>75.09</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>86.86</v>
+        <v>86.73</v>
       </c>
       <c r="E10" s="31" t="n">
         <v>58.44</v>
       </c>
       <c r="F10" s="31" t="n">
-        <v>50.06</v>
+        <v>49.99</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>90.37</v>
+        <v>90.41</v>
       </c>
       <c r="H10" s="31" t="n">
         <v>55</v>
       </c>
       <c r="I10" s="32" t="n">
-        <v>69.68000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J10" s="32" t="n">
-        <v>66.38</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="K10" s="31" t="n">
         <v>51.4</v>
@@ -16622,22 +16622,22 @@
         <v>100</v>
       </c>
       <c r="M10" s="30" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="N10" s="33" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="O10" s="32" t="n">
         <v>70</v>
       </c>
       <c r="P10" s="30" t="n">
-        <v>84.75</v>
+        <v>83.64</v>
       </c>
       <c r="Q10" s="31" t="n">
         <v>50</v>
       </c>
       <c r="R10" s="33" t="n">
-        <v>5.76</v>
+        <v>5.3</v>
       </c>
       <c r="S10" s="30" t="n">
         <v>100</v>
@@ -16667,16 +16667,16 @@
         <v>82.5</v>
       </c>
       <c r="AB10" s="32" t="n">
-        <v>78.20999999999999</v>
+        <v>77.84</v>
       </c>
       <c r="AC10" s="30" t="n">
         <v>100</v>
       </c>
       <c r="AD10" s="32" t="n">
-        <v>76.59</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="AE10" s="32" t="n">
-        <v>78.47</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="AF10" s="30" t="n">
         <v>88</v>
@@ -16797,28 +16797,28 @@
         </is>
       </c>
       <c r="C11" s="35" t="n">
-        <v>74.7</v>
+        <v>74.59</v>
       </c>
       <c r="D11" s="32" t="n">
-        <v>70.76000000000001</v>
+        <v>70.47</v>
       </c>
       <c r="E11" s="31" t="n">
-        <v>58.39</v>
+        <v>57.47</v>
       </c>
       <c r="F11" s="32" t="n">
-        <v>71.14</v>
+        <v>71.06</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>90.22</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H11" s="31" t="n">
         <v>57.67</v>
       </c>
       <c r="I11" s="32" t="n">
-        <v>78.23</v>
+        <v>78.2</v>
       </c>
       <c r="J11" s="32" t="n">
-        <v>66.38</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="K11" s="32" t="n">
         <v>61.98</v>
@@ -16827,22 +16827,22 @@
         <v>100</v>
       </c>
       <c r="M11" s="30" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="N11" s="33" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="O11" s="32" t="n">
         <v>70</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>54.24</v>
+        <v>50.93</v>
       </c>
       <c r="Q11" s="32" t="n">
         <v>70</v>
       </c>
       <c r="R11" s="31" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="S11" s="30" t="n">
         <v>100</v>
@@ -16860,7 +16860,7 @@
         <v>100</v>
       </c>
       <c r="X11" s="30" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="Y11" s="30" t="n">
         <v>85.09999999999999</v>
@@ -16872,22 +16872,22 @@
         <v>86.25</v>
       </c>
       <c r="AB11" s="33" t="n">
-        <v>19.55</v>
+        <v>19.46</v>
       </c>
       <c r="AC11" s="30" t="n">
         <v>80</v>
       </c>
       <c r="AD11" s="32" t="n">
-        <v>76.59</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="AE11" s="31" t="n">
-        <v>53.48</v>
+        <v>53.67</v>
       </c>
       <c r="AF11" s="30" t="n">
         <v>88</v>
       </c>
       <c r="AG11" s="30" t="n">
-        <v>89.95</v>
+        <v>89.98</v>
       </c>
       <c r="AH11" s="30" t="n">
         <v>100</v>
@@ -17002,28 +17002,28 @@
         </is>
       </c>
       <c r="C12" s="35" t="n">
-        <v>69.78</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="D12" s="32" t="n">
-        <v>74.93000000000001</v>
+        <v>74.91</v>
       </c>
       <c r="E12" s="31" t="n">
         <v>58.44</v>
       </c>
       <c r="F12" s="31" t="n">
-        <v>50.06</v>
+        <v>49.99</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>90.7</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="H12" s="31" t="n">
         <v>51.73</v>
       </c>
       <c r="I12" s="32" t="n">
-        <v>70.68000000000001</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="J12" s="32" t="n">
-        <v>67.63</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="K12" s="31" t="n">
         <v>51.4</v>
@@ -17032,22 +17032,22 @@
         <v>100</v>
       </c>
       <c r="M12" s="30" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="N12" s="33" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="O12" s="32" t="n">
         <v>70</v>
       </c>
       <c r="P12" s="30" t="n">
-        <v>98.47</v>
+        <v>98.36</v>
       </c>
       <c r="Q12" s="31" t="n">
         <v>50</v>
       </c>
       <c r="R12" s="33" t="n">
-        <v>5.76</v>
+        <v>5.3</v>
       </c>
       <c r="S12" s="30" t="n">
         <v>100</v>
@@ -17077,16 +17077,16 @@
         <v>82.5</v>
       </c>
       <c r="AB12" s="33" t="n">
-        <v>19.55</v>
+        <v>19.46</v>
       </c>
       <c r="AC12" s="30" t="n">
         <v>100</v>
       </c>
       <c r="AD12" s="30" t="n">
-        <v>85.59</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="AE12" s="30" t="n">
-        <v>81.13</v>
+        <v>81.41</v>
       </c>
       <c r="AF12" s="30" t="n">
         <v>88</v>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>83.0 / 100</t>
+          <t>82.9 / 100</t>
         </is>
       </c>
       <c r="D4" s="28" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>RVG29-PLGA-NP: composite CNS-principle score = 83.0/100 (EXCELLENT). Carrier: plga, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G4 Safety (91.6/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>RVG29-PLGA-NP: composite CNS-principle score = 82.9/100 (EXCELLENT). Carrier: plga, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G4 Safety (91.6/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -17278,7 +17278,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 88/100  G2_Release_Kinetics: 58/100  G3_Stability: 71/100  G4_Safety: 92/100  G5_Glymphatic_BBB: 62/100  G6_Manufacturability: 81/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 88/100  G2_Release_Kinetics: 57/100  G3_Stability: 71/100  G4_Safety: 92/100  G5_Glymphatic_BBB: 62/100  G6_Manufacturability: 81/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>82.0 / 100</t>
+          <t>81.9 / 100</t>
         </is>
       </c>
       <c r="D14" s="28" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>Tf-SLN-Stealth: composite CNS-principle score = 82.0/100 (EXCELLENT). Carrier: solid_lipid, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G4 Safety (91.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>Tf-SLN-Stealth: composite CNS-principle score = 81.9/100 (EXCELLENT). Carrier: solid_lipid, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G4 Safety (91.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 88/100  G2_Release_Kinetics: 59/100  G3_Stability: 69/100  G4_Safety: 92/100  G5_Glymphatic_BBB: 57/100  G6_Manufacturability: 73/100  G7_DrugDDS_Fit: 70/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 88/100  G2_Release_Kinetics: 58/100  G3_Stability: 69/100  G4_Safety: 92/100  G5_Glymphatic_BBB: 57/100  G6_Manufacturability: 73/100  G7_DrugDDS_Fit: 70/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>81.7 / 100</t>
+          <t>81.6 / 100</t>
         </is>
       </c>
       <c r="D24" s="28" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>ApoE-SLN: composite CNS-principle score = 81.7/100 (EXCELLENT). Carrier: solid_lipid, size 0.0 nm, ζ +0.0 mV, ligand: ApoE. Strongest group: G4 Safety (91.2/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>ApoE-SLN: composite CNS-principle score = 81.6/100 (EXCELLENT). Carrier: solid_lipid, size 0.0 nm, ζ +0.0 mV, ligand: ApoE. Strongest group: G4 Safety (91.2/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 87/100  G2_Release_Kinetics: 59/100  G3_Stability: 69/100  G4_Safety: 91/100  G5_Glymphatic_BBB: 57/100  G6_Manufacturability: 73/100  G7_DrugDDS_Fit: 70/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 87/100  G2_Release_Kinetics: 58/100  G3_Stability: 69/100  G4_Safety: 91/100  G5_Glymphatic_BBB: 57/100  G6_Manufacturability: 73/100  G7_DrugDDS_Fit: 70/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -17687,7 +17687,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>81.0 / 100</t>
+          <t>80.9 / 100</t>
         </is>
       </c>
       <c r="D34" s="28" t="inlineStr">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>RVG29-Liposome-pH: composite CNS-principle score = 81.0/100 (EXCELLENT). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G4 Safety (91.4/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>RVG29-Liposome-pH: composite CNS-principle score = 80.9/100 (EXCELLENT). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G4 Safety (91.4/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -17716,7 +17716,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 89/100  G2_Release_Kinetics: 59/100  G3_Stability: 51/100  G4_Safety: 91/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 68/100  G7_DrugDDS_Fit: 68/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 89/100  G2_Release_Kinetics: 58/100  G3_Stability: 51/100  G4_Safety: 91/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 68/100  G7_DrugDDS_Fit: 68/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>16.1/100</t>
+          <t>18.1/100</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>80.2 / 100</t>
+          <t>80.1 / 100</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Tf-PEG-Liposome-Donepezil: composite CNS-principle score = 80.2/100 (EXCELLENT). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G4 Safety (92.2/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>Tf-PEG-Liposome-Donepezil: composite CNS-principle score = 80.1/100 (EXCELLENT). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G4 Safety (92.2/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -17862,7 +17862,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 87/100  G2_Release_Kinetics: 59/100  G3_Stability: 51/100  G4_Safety: 92/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 69/100  G7_DrugDDS_Fit: 67/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 87/100  G2_Release_Kinetics: 58/100  G3_Stability: 51/100  G4_Safety: 92/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 69/100  G7_DrugDDS_Fit: 67/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>16.1/100</t>
+          <t>18.1/100</t>
         </is>
       </c>
       <c r="D51" s="22" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 87/100  G2_Release_Kinetics: 58/100  G3_Stability: 50/100  G4_Safety: 90/100  G5_Glymphatic_BBB: 55/100  G6_Manufacturability: 70/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 87/100  G2_Release_Kinetics: 58/100  G3_Stability: 50/100  G4_Safety: 90/100  G5_Glymphatic_BBB: 55/100  G6_Manufacturability: 70/100  G7_DrugDDS_Fit: 67/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -18064,7 +18064,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -18074,24 +18074,24 @@
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: WKB tunneling: P ∝ exp(-2·barrier)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>16.1/100</t>
+          <t>18.1/100</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: WKB tunneling: P ∝ exp(-2·barrier)</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
         </is>
       </c>
     </row>
@@ -18125,7 +18125,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>74.7 / 100</t>
+          <t>74.6 / 100</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Bare-PLGA: composite CNS-principle score = 74.7/100 (GOOD). Carrier: plga, size 0.0 nm, ζ +0.0 mV, ligand: None. Strongest group: G4 Safety (90.2/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>Bare-PLGA: composite CNS-principle score = 74.6/100 (GOOD). Carrier: plga, size 0.0 nm, ζ +0.0 mV, ligand: None. Strongest group: G4 Safety (90.2/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -18154,7 +18154,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 71/100  G2_Release_Kinetics: 58/100  G3_Stability: 71/100  G4_Safety: 90/100  G5_Glymphatic_BBB: 58/100  G6_Manufacturability: 78/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 70/100  G2_Release_Kinetics: 57/100  G3_Stability: 71/100  G4_Safety: 90/100  G5_Glymphatic_BBB: 58/100  G6_Manufacturability: 78/100  G7_DrugDDS_Fit: 67/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>19.6/100</t>
+          <t>19.5/100</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -18366,24 +18366,24 @@
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: WKB tunneling: P ∝ exp(-2·barrier)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>16.1/100</t>
+          <t>18.1/100</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: WKB tunneling: P ∝ exp(-2·barrier)</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
         </is>
       </c>
     </row>
@@ -18660,11 +18660,11 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>83.05</v>
+        <v>83.97</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>83.97</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -18701,11 +18701,11 @@
         </is>
       </c>
       <c r="E8" s="41" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -18783,11 +18783,11 @@
         </is>
       </c>
       <c r="E10" s="40" t="n">
-        <v>72.54000000000001</v>
+        <v>70.56</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>70.56</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -18865,11 +18865,11 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -19111,11 +19111,11 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -19275,11 +19275,11 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>87.98</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -19357,11 +19357,11 @@
         </is>
       </c>
       <c r="E24" s="40" t="n">
-        <v>61.59</v>
+        <v>61.29</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.59</t>
+          <t>61.29</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -19398,11 +19398,11 @@
         </is>
       </c>
       <c r="E25" s="40" t="n">
-        <v>64.25</v>
+        <v>64.47</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>64.25</t>
+          <t>64.47</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -19480,11 +19480,11 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>89.95</v>
+        <v>89.98</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -20997,11 +20997,11 @@
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>98.05</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -21038,11 +21038,11 @@
         </is>
       </c>
       <c r="E65" s="41" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -21120,11 +21120,11 @@
         </is>
       </c>
       <c r="E67" s="7" t="n">
-        <v>90.84999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>90.85</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -21202,11 +21202,11 @@
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>35.76</v>
+        <v>35.3</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>35.76</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -21448,11 +21448,11 @@
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -21612,11 +21612,11 @@
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>81.73</v>
+        <v>81.34</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.34</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -21694,11 +21694,11 @@
         </is>
       </c>
       <c r="E81" s="40" t="n">
-        <v>70.59</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>70.29</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -21735,11 +21735,11 @@
         </is>
       </c>
       <c r="E82" s="40" t="n">
-        <v>73.41</v>
+        <v>73.66</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -23334,11 +23334,11 @@
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>98.05</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -23375,11 +23375,11 @@
         </is>
       </c>
       <c r="E122" s="41" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -23457,11 +23457,11 @@
         </is>
       </c>
       <c r="E124" s="40" t="n">
-        <v>78.65000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>78.65</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -23539,11 +23539,11 @@
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>35.76</v>
+        <v>35.3</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>35.76</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E132" s="7" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -23949,11 +23949,11 @@
         </is>
       </c>
       <c r="E136" s="7" t="n">
-        <v>86.02</v>
+        <v>84.86</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>84.86</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -24031,11 +24031,11 @@
         </is>
       </c>
       <c r="E138" s="40" t="n">
-        <v>67.59</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>67.59</t>
+          <t>67.29</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -24072,11 +24072,11 @@
         </is>
       </c>
       <c r="E139" s="40" t="n">
-        <v>68.67</v>
+        <v>68.91</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -25671,11 +25671,11 @@
         </is>
       </c>
       <c r="E178" s="7" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>98.05</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -25712,11 +25712,11 @@
         </is>
       </c>
       <c r="E179" s="41" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -25794,11 +25794,11 @@
         </is>
       </c>
       <c r="E181" s="7" t="n">
-        <v>84.75</v>
+        <v>83.64</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -25876,11 +25876,11 @@
         </is>
       </c>
       <c r="E183" s="41" t="n">
-        <v>13.26</v>
+        <v>12.8</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -26122,11 +26122,11 @@
         </is>
       </c>
       <c r="E189" s="7" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -26286,11 +26286,11 @@
         </is>
       </c>
       <c r="E193" s="7" t="n">
-        <v>87.98</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -26368,11 +26368,11 @@
         </is>
       </c>
       <c r="E195" s="40" t="n">
-        <v>67.59</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>67.59</t>
+          <t>67.29</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -26409,11 +26409,11 @@
         </is>
       </c>
       <c r="E196" s="40" t="n">
-        <v>69.25</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.25</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -28008,11 +28008,11 @@
         </is>
       </c>
       <c r="E235" s="40" t="n">
-        <v>78.05</v>
+        <v>78.97</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>78.05</t>
+          <t>78.97</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -28049,11 +28049,11 @@
         </is>
       </c>
       <c r="E236" s="41" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -28131,11 +28131,11 @@
         </is>
       </c>
       <c r="E238" s="7" t="n">
-        <v>84.75</v>
+        <v>83.64</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -28213,11 +28213,11 @@
         </is>
       </c>
       <c r="E240" s="41" t="n">
-        <v>13.26</v>
+        <v>12.8</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -28459,11 +28459,11 @@
         </is>
       </c>
       <c r="E246" s="7" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -28623,11 +28623,11 @@
         </is>
       </c>
       <c r="E250" s="7" t="n">
-        <v>81.73</v>
+        <v>81.34</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.34</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -28705,11 +28705,11 @@
         </is>
       </c>
       <c r="E252" s="40" t="n">
-        <v>73.59</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -28746,11 +28746,11 @@
         </is>
       </c>
       <c r="E253" s="40" t="n">
-        <v>75.27</v>
+        <v>75.53</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>75.27</t>
+          <t>75.53</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -30345,11 +30345,11 @@
         </is>
       </c>
       <c r="E292" s="7" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>98.05</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -30386,11 +30386,11 @@
         </is>
       </c>
       <c r="E293" s="41" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -30468,11 +30468,11 @@
         </is>
       </c>
       <c r="E295" s="7" t="n">
-        <v>84.75</v>
+        <v>83.64</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -30550,11 +30550,11 @@
         </is>
       </c>
       <c r="E297" s="41" t="n">
-        <v>5.76</v>
+        <v>5.3</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -30960,11 +30960,11 @@
         </is>
       </c>
       <c r="E307" s="40" t="n">
-        <v>78.20999999999999</v>
+        <v>77.84</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>78.21</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -31042,11 +31042,11 @@
         </is>
       </c>
       <c r="E309" s="40" t="n">
-        <v>76.59</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>76.29</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -31083,11 +31083,11 @@
         </is>
       </c>
       <c r="E310" s="40" t="n">
-        <v>78.47</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>78.47</t>
+          <t>78.74</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -32682,11 +32682,11 @@
         </is>
       </c>
       <c r="E349" s="7" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>98.05</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -32723,11 +32723,11 @@
         </is>
       </c>
       <c r="E350" s="41" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -32805,11 +32805,11 @@
         </is>
       </c>
       <c r="E352" s="8" t="n">
-        <v>54.24</v>
+        <v>50.93</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>50.93</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -32887,11 +32887,11 @@
         </is>
       </c>
       <c r="E354" s="8" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -33133,11 +33133,11 @@
         </is>
       </c>
       <c r="E360" s="7" t="n">
-        <v>98.56</v>
+        <v>94.86</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="G360" s="5" t="inlineStr">
@@ -33297,11 +33297,11 @@
         </is>
       </c>
       <c r="E364" s="41" t="n">
-        <v>19.55</v>
+        <v>19.46</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="G364" s="5" t="inlineStr">
@@ -33379,11 +33379,11 @@
         </is>
       </c>
       <c r="E366" s="40" t="n">
-        <v>76.59</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>76.29</t>
         </is>
       </c>
       <c r="G366" s="5" t="inlineStr">
@@ -33420,11 +33420,11 @@
         </is>
       </c>
       <c r="E367" s="8" t="n">
-        <v>53.48</v>
+        <v>53.67</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>53.67</t>
         </is>
       </c>
       <c r="G367" s="5" t="inlineStr">
@@ -33502,11 +33502,11 @@
         </is>
       </c>
       <c r="E369" s="7" t="n">
-        <v>89.95</v>
+        <v>89.98</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="G369" s="5" t="inlineStr">
@@ -35019,11 +35019,11 @@
         </is>
       </c>
       <c r="E406" s="7" t="n">
-        <v>98.05</v>
+        <v>98.97</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>98.05</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="G406" s="5" t="inlineStr">
@@ -35060,11 +35060,11 @@
         </is>
       </c>
       <c r="E407" s="41" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="G407" s="5" t="inlineStr">
@@ -35142,11 +35142,11 @@
         </is>
       </c>
       <c r="E409" s="7" t="n">
-        <v>98.47</v>
+        <v>98.36</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>98.47</t>
+          <t>98.36</t>
         </is>
       </c>
       <c r="G409" s="5" t="inlineStr">
@@ -35224,11 +35224,11 @@
         </is>
       </c>
       <c r="E411" s="41" t="n">
-        <v>5.76</v>
+        <v>5.3</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="G411" s="5" t="inlineStr">
@@ -35634,11 +35634,11 @@
         </is>
       </c>
       <c r="E421" s="41" t="n">
-        <v>19.55</v>
+        <v>19.46</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="G421" s="5" t="inlineStr">
@@ -35716,11 +35716,11 @@
         </is>
       </c>
       <c r="E423" s="7" t="n">
-        <v>85.59</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>85.59</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="G423" s="5" t="inlineStr">
@@ -35757,11 +35757,11 @@
         </is>
       </c>
       <c r="E424" s="7" t="n">
-        <v>81.13</v>
+        <v>81.41</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>81.13</t>
+          <t>81.41</t>
         </is>
       </c>
       <c r="G424" s="5" t="inlineStr">
@@ -37436,20 +37436,20 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>19.65</v>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>Resolved clinical half-life (bundle tier 1); Mahmood 2007 exponents shown for reference only (half-life ~ BW^0.25, clearance ~ BW^0.75, volume ~ BW^1.0) -- not applied, since no animal PK value exists</t>
+          <t>Resolved clinical half-life (bundle tier 6); Mahmood 2007 exponents shown for reference only (half-life ~ BW^0.25, clearance ~ BW^0.75, volume ~ BW^1.0) -- not applied, since no animal PK value exists</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -37459,7 +37459,7 @@
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t>Clinical t½ = 1.5h (human clinical source, bundle tier 1). Reference allometric exponents (Mahmood 2007) for a genuine animal-to-human extrapolation, if one were available: clearance ~384.9×, volume ~</t>
+          <t>Clinical t½ = 19.6h (population regression / class estimate, bundle tier 6). Reference allometric exponents (Mahmood 2007) for a genuine animal-to-human extrapolation, if one were available: clearance</t>
         </is>
       </c>
     </row>
@@ -37475,10 +37475,10 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>16.09</v>
+        <v>18.14</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0805</v>
+        <v>0.0907</v>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>Full QM tunneling (QCElemental + ASE): surrogate score 16.09 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full QM tunneling (QCElemental + ASE): surrogate score 18.14 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -37514,10 +37514,10 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="D13" t="n">
-        <v>58.26</v>
+        <v>57.8</v>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Full radical-chain reaction MD: surrogate score 58.26 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full radical-chain reaction MD: surrogate score 57.8 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -37766,7 +37766,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>Surrogate: lookup score 87.98. Deep: ΔG_bind = -9.8 kcal/mol vs receptor nAChR.</t>
+          <t>Surrogate: lookup score 87.57. Deep: ΔG_bind = -9.8 kcal/mol vs receptor nAChR.</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -37826,10 +37826,10 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>89.95</v>
+        <v>89.98</v>
       </c>
       <c r="D21" t="n">
-        <v>89.95</v>
+        <v>89.98</v>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
       </c>
       <c r="I21" s="22" t="inlineStr">
         <is>
-          <t>Full CFD + MD coupling: surrogate score 89.95 PASSED. Full deep simulation requires external HPC.</t>
+          <t>Full CFD + MD coupling: surrogate score 89.98 PASSED. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -38216,10 +38216,10 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>79.2</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-7.2</v>
+        <v>-7.12</v>
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
@@ -38234,12 +38234,12 @@
       </c>
       <c r="H31" s="22" t="inlineStr">
         <is>
-          <t>Surrogate ΔG: 90.0 → Deep ΔG: -7.20 kcal/mol via LIE approximation (no receptor PDB ID resolved yet).</t>
+          <t>Surrogate ΔG: 90.0 → Deep ΔG: -7.12 kcal/mol via LIE approximation (no receptor PDB ID resolved yet).</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
         <is>
-          <t>Predicted ΔG_binding = -7.20 kcal/mol (LIE approximation (fallback — Vina unavailable)). MODERATE affinity.</t>
+          <t>Predicted ΔG_binding = -7.12 kcal/mol (LIE approximation (fallback — Vina unavailable)). MODERATE affinity.</t>
         </is>
       </c>
     </row>
